--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2024_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2024_magallanes.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:08</t>
+    <t xml:space="preserve">2026-09-24 01:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,19 +561,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.45</v>
+        <v>-0.29</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.61</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="3">
@@ -584,19 +584,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.67</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.27</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="4">
@@ -607,19 +607,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.31</v>
+        <v>-0.33</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="5">
@@ -630,19 +630,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.71</v>
+        <v>-0.31</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="6">
@@ -653,19 +653,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="7">
@@ -885,19 +885,19 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.66</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="19">
@@ -908,19 +908,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="20">
@@ -931,19 +931,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="21">
@@ -954,19 +954,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="22">
@@ -977,19 +977,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.57</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.31</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="23">
@@ -1000,19 +1000,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
